--- a/output/yearly_population_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_23_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5600</v>
+        <v>5743</v>
       </c>
       <c r="C2" t="n">
-        <v>8918</v>
+        <v>6903</v>
       </c>
       <c r="D2" t="n">
-        <v>24224</v>
+        <v>21270</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3305</v>
+        <v>3938</v>
       </c>
       <c r="C3" t="n">
-        <v>5465</v>
+        <v>5384</v>
       </c>
       <c r="D3" t="n">
-        <v>12374</v>
+        <v>17225</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2421</v>
+        <v>3163</v>
       </c>
       <c r="C4" t="n">
-        <v>3900</v>
+        <v>5093</v>
       </c>
       <c r="D4" t="n">
-        <v>7250</v>
+        <v>8738</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1686</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>3346</v>
+        <v>4834</v>
       </c>
       <c r="D5" t="n">
-        <v>2944</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>1102</v>
       </c>
       <c r="C6" t="n">
-        <v>2167</v>
+        <v>3334</v>
       </c>
       <c r="D6" t="n">
-        <v>1204</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>1251</v>
+        <v>2007</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>605</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>430</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8348</v>
+        <v>7759</v>
       </c>
       <c r="C2" t="n">
-        <v>7033</v>
+        <v>11536</v>
       </c>
       <c r="D2" t="n">
-        <v>24154</v>
+        <v>34203</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3548</v>
+        <v>3850</v>
       </c>
       <c r="C3" t="n">
-        <v>6247</v>
+        <v>5338</v>
       </c>
       <c r="D3" t="n">
-        <v>13229</v>
+        <v>16612</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2435</v>
+        <v>2985</v>
       </c>
       <c r="C4" t="n">
-        <v>4615</v>
+        <v>5072</v>
       </c>
       <c r="D4" t="n">
-        <v>7915</v>
+        <v>9692</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1785</v>
+        <v>2230</v>
       </c>
       <c r="C5" t="n">
-        <v>3515</v>
+        <v>4850</v>
       </c>
       <c r="D5" t="n">
-        <v>3528</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1205</v>
+        <v>1344</v>
       </c>
       <c r="C6" t="n">
-        <v>2710</v>
+        <v>3917</v>
       </c>
       <c r="D6" t="n">
-        <v>1471</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C7" t="n">
-        <v>1681</v>
+        <v>2578</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="C8" t="n">
-        <v>890</v>
+        <v>1410</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>433</v>
+        <v>663</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10034</v>
+        <v>8081</v>
       </c>
       <c r="C2" t="n">
-        <v>7154</v>
+        <v>12963</v>
       </c>
       <c r="D2" t="n">
-        <v>20242</v>
+        <v>35569</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4485</v>
+        <v>4333</v>
       </c>
       <c r="C3" t="n">
-        <v>5875</v>
+        <v>6930</v>
       </c>
       <c r="D3" t="n">
-        <v>13759</v>
+        <v>17659</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2474</v>
+        <v>2833</v>
       </c>
       <c r="C4" t="n">
-        <v>5226</v>
+        <v>5078</v>
       </c>
       <c r="D4" t="n">
-        <v>8414</v>
+        <v>10393</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1831</v>
+        <v>2250</v>
       </c>
       <c r="C5" t="n">
-        <v>3904</v>
+        <v>4792</v>
       </c>
       <c r="D5" t="n">
-        <v>4094</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1328</v>
+        <v>1532</v>
       </c>
       <c r="C6" t="n">
-        <v>3039</v>
+        <v>4212</v>
       </c>
       <c r="D6" t="n">
-        <v>1733</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="C7" t="n">
-        <v>2107</v>
+        <v>3101</v>
       </c>
       <c r="D7" t="n">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="C8" t="n">
-        <v>1222</v>
+        <v>1830</v>
       </c>
       <c r="D8" t="n">
-        <v>498</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>612</v>
+        <v>927</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>427</v>
       </c>
       <c r="D10" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8916</v>
+        <v>7470</v>
       </c>
       <c r="C2" t="n">
-        <v>4693</v>
+        <v>9022</v>
       </c>
       <c r="D2" t="n">
-        <v>16427</v>
+        <v>29302</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5050</v>
+        <v>5108</v>
       </c>
       <c r="C3" t="n">
-        <v>8626</v>
+        <v>10145</v>
       </c>
       <c r="D3" t="n">
-        <v>15478</v>
+        <v>19297</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1691</v>
+        <v>2079</v>
       </c>
       <c r="C4" t="n">
-        <v>6808</v>
+        <v>7330</v>
       </c>
       <c r="D4" t="n">
-        <v>8363</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1227</v>
+        <v>1415</v>
       </c>
       <c r="C5" t="n">
-        <v>2978</v>
+        <v>4127</v>
       </c>
       <c r="D5" t="n">
-        <v>2838</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="C6" t="n">
-        <v>2064</v>
+        <v>3038</v>
       </c>
       <c r="D6" t="n">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="C7" t="n">
-        <v>1197</v>
+        <v>1793</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>599</v>
+        <v>908</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5323</v>
+        <v>4560</v>
       </c>
       <c r="C2" t="n">
-        <v>1906</v>
+        <v>3863</v>
       </c>
       <c r="D2" t="n">
-        <v>11872</v>
+        <v>20727</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5749</v>
+        <v>5246</v>
       </c>
       <c r="C3" t="n">
-        <v>6085</v>
+        <v>8770</v>
       </c>
       <c r="D3" t="n">
-        <v>14846</v>
+        <v>19731</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2600</v>
+        <v>2782</v>
       </c>
       <c r="C4" t="n">
-        <v>7817</v>
+        <v>8729</v>
       </c>
       <c r="D4" t="n">
-        <v>9281</v>
+        <v>11182</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1352</v>
+        <v>1575</v>
       </c>
       <c r="C5" t="n">
-        <v>4713</v>
+        <v>5460</v>
       </c>
       <c r="D5" t="n">
-        <v>3548</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="C6" t="n">
-        <v>2502</v>
+        <v>3589</v>
       </c>
       <c r="D6" t="n">
-        <v>1054</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>1556</v>
+        <v>2250</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>789</v>
+        <v>1190</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>451</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5066</v>
+        <v>4310</v>
       </c>
       <c r="C2" t="n">
-        <v>5841</v>
+        <v>4195</v>
       </c>
       <c r="D2" t="n">
-        <v>16610</v>
+        <v>16494</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4659</v>
+        <v>4177</v>
       </c>
       <c r="C3" t="n">
-        <v>3525</v>
+        <v>5754</v>
       </c>
       <c r="D3" t="n">
-        <v>13396</v>
+        <v>18540</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3462</v>
+        <v>3257</v>
       </c>
       <c r="C4" t="n">
-        <v>6756</v>
+        <v>8567</v>
       </c>
       <c r="D4" t="n">
-        <v>9960</v>
+        <v>12237</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1682</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>6209</v>
+        <v>6905</v>
       </c>
       <c r="D5" t="n">
-        <v>4375</v>
+        <v>4811</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>1085</v>
       </c>
       <c r="C6" t="n">
-        <v>3516</v>
+        <v>4363</v>
       </c>
       <c r="D6" t="n">
-        <v>1422</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>2006</v>
+        <v>2835</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>1616</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>548</v>
+        <v>723</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2940</v>
+        <v>2607</v>
       </c>
       <c r="C2" t="n">
-        <v>2601</v>
+        <v>2030</v>
       </c>
       <c r="D2" t="n">
-        <v>11471</v>
+        <v>11505</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4590</v>
+        <v>4097</v>
       </c>
       <c r="C3" t="n">
-        <v>4234</v>
+        <v>5076</v>
       </c>
       <c r="D3" t="n">
-        <v>13434</v>
+        <v>17911</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3864</v>
+        <v>3560</v>
       </c>
       <c r="C4" t="n">
-        <v>6116</v>
+        <v>8402</v>
       </c>
       <c r="D4" t="n">
-        <v>10465</v>
+        <v>13043</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>1918</v>
       </c>
       <c r="C5" t="n">
-        <v>7208</v>
+        <v>8307</v>
       </c>
       <c r="D5" t="n">
-        <v>4721</v>
+        <v>5076</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>4408</v>
+        <v>5186</v>
       </c>
       <c r="D6" t="n">
-        <v>1397</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2105</v>
+        <v>2942</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>912</v>
+        <v>1183</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3930</v>
+        <v>3264</v>
       </c>
       <c r="C2" t="n">
-        <v>4183</v>
+        <v>4439</v>
       </c>
       <c r="D2" t="n">
-        <v>12593</v>
+        <v>18799</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3318</v>
+        <v>2998</v>
       </c>
       <c r="C3" t="n">
-        <v>3053</v>
+        <v>3329</v>
       </c>
       <c r="D3" t="n">
-        <v>12356</v>
+        <v>16008</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3644</v>
+        <v>3297</v>
       </c>
       <c r="C4" t="n">
-        <v>5108</v>
+        <v>6775</v>
       </c>
       <c r="D4" t="n">
-        <v>10631</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2334</v>
+        <v>2284</v>
       </c>
       <c r="C5" t="n">
-        <v>6613</v>
+        <v>8175</v>
       </c>
       <c r="D5" t="n">
-        <v>5459</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="C6" t="n">
-        <v>5645</v>
+        <v>6529</v>
       </c>
       <c r="D6" t="n">
-        <v>1857</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>3115</v>
+        <v>3827</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1826</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>503</v>
+        <v>585</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>43</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2751</v>
+        <v>2385</v>
       </c>
       <c r="C2" t="n">
-        <v>2688</v>
+        <v>3106</v>
       </c>
       <c r="D2" t="n">
-        <v>9610</v>
+        <v>15088</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3085</v>
+        <v>2701</v>
       </c>
       <c r="C3" t="n">
-        <v>3218</v>
+        <v>3412</v>
       </c>
       <c r="D3" t="n">
-        <v>11694</v>
+        <v>15475</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3233</v>
+        <v>2959</v>
       </c>
       <c r="C4" t="n">
-        <v>4261</v>
+        <v>5472</v>
       </c>
       <c r="D4" t="n">
-        <v>10760</v>
+        <v>13441</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2609</v>
+        <v>2447</v>
       </c>
       <c r="C5" t="n">
-        <v>6151</v>
+        <v>7756</v>
       </c>
       <c r="D5" t="n">
-        <v>5941</v>
+        <v>6773</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1373</v>
+        <v>1335</v>
       </c>
       <c r="C6" t="n">
-        <v>6196</v>
+        <v>7295</v>
       </c>
       <c r="D6" t="n">
-        <v>2234</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>3996</v>
+        <v>4723</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1821</v>
+        <v>2314</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>621</v>
+        <v>659</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5363</v>
+        <v>3105</v>
       </c>
       <c r="C2" t="n">
-        <v>8895</v>
+        <v>10342</v>
       </c>
       <c r="D2" t="n">
-        <v>11792</v>
+        <v>22124</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2487</v>
+        <v>2182</v>
       </c>
       <c r="C3" t="n">
-        <v>2648</v>
+        <v>2935</v>
       </c>
       <c r="D3" t="n">
-        <v>10660</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2761</v>
+        <v>2494</v>
       </c>
       <c r="C4" t="n">
-        <v>3701</v>
+        <v>4507</v>
       </c>
       <c r="D4" t="n">
-        <v>10576</v>
+        <v>13176</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2606</v>
+        <v>2414</v>
       </c>
       <c r="C5" t="n">
-        <v>5206</v>
+        <v>6695</v>
       </c>
       <c r="D5" t="n">
-        <v>6454</v>
+        <v>7463</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1683</v>
+        <v>1578</v>
       </c>
       <c r="C6" t="n">
-        <v>6121</v>
+        <v>7407</v>
       </c>
       <c r="D6" t="n">
-        <v>2703</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>626</v>
+        <v>530</v>
       </c>
       <c r="C7" t="n">
-        <v>4917</v>
+        <v>5653</v>
       </c>
       <c r="D7" t="n">
-        <v>977</v>
+        <v>911</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>2630</v>
+        <v>3162</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1050</v>
+        <v>1184</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5669</v>
+        <v>6464</v>
       </c>
       <c r="C2" t="n">
-        <v>3596</v>
+        <v>10927</v>
       </c>
       <c r="D2" t="n">
-        <v>13344</v>
+        <v>15992</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3750</v>
+        <v>2247</v>
       </c>
       <c r="C2" t="n">
-        <v>4911</v>
+        <v>6040</v>
       </c>
       <c r="D2" t="n">
-        <v>8584</v>
+        <v>16461</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3500</v>
+        <v>2936</v>
       </c>
       <c r="C3" t="n">
-        <v>4417</v>
+        <v>4797</v>
       </c>
       <c r="D3" t="n">
-        <v>11691</v>
+        <v>16126</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3816</v>
+        <v>3482</v>
       </c>
       <c r="C4" t="n">
-        <v>5382</v>
+        <v>6765</v>
       </c>
       <c r="D4" t="n">
-        <v>11030</v>
+        <v>13554</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1675</v>
+        <v>1502</v>
       </c>
       <c r="C5" t="n">
-        <v>8177</v>
+        <v>10121</v>
       </c>
       <c r="D5" t="n">
-        <v>6006</v>
+        <v>6744</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>578</v>
+        <v>489</v>
       </c>
       <c r="C6" t="n">
-        <v>6138</v>
+        <v>6919</v>
       </c>
       <c r="D6" t="n">
-        <v>2174</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>2577</v>
+        <v>3098</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1029</v>
+        <v>1160</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6332</v>
+        <v>6775</v>
       </c>
       <c r="C2" t="n">
-        <v>4579</v>
+        <v>5995</v>
       </c>
       <c r="D2" t="n">
-        <v>16179</v>
+        <v>22395</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2409</v>
+        <v>2746</v>
       </c>
       <c r="C3" t="n">
-        <v>1812</v>
+        <v>5507</v>
       </c>
       <c r="D3" t="n">
-        <v>2881</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5499</v>
+        <v>6219</v>
       </c>
       <c r="C2" t="n">
-        <v>4172</v>
+        <v>4500</v>
       </c>
       <c r="D2" t="n">
-        <v>17630</v>
+        <v>24125</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3589</v>
+        <v>3910</v>
       </c>
       <c r="C3" t="n">
-        <v>2949</v>
+        <v>4987</v>
       </c>
       <c r="D3" t="n">
-        <v>4903</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1080</v>
+        <v>1227</v>
       </c>
       <c r="C4" t="n">
-        <v>1106</v>
+        <v>3270</v>
       </c>
       <c r="D4" t="n">
-        <v>1761</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4595</v>
+        <v>4906</v>
       </c>
       <c r="C2" t="n">
-        <v>4738</v>
+        <v>7599</v>
       </c>
       <c r="D2" t="n">
-        <v>26519</v>
+        <v>22680</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>4170</v>
       </c>
       <c r="C3" t="n">
-        <v>3129</v>
+        <v>4098</v>
       </c>
       <c r="D3" t="n">
-        <v>6586</v>
+        <v>8686</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1976</v>
+        <v>2153</v>
       </c>
       <c r="C4" t="n">
-        <v>2116</v>
+        <v>4158</v>
       </c>
       <c r="D4" t="n">
-        <v>2310</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="C5" t="n">
-        <v>709</v>
+        <v>1855</v>
       </c>
       <c r="D5" t="n">
-        <v>1243</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4698</v>
+        <v>7482</v>
       </c>
       <c r="C2" t="n">
-        <v>5531</v>
+        <v>11208</v>
       </c>
       <c r="D2" t="n">
-        <v>28947</v>
+        <v>35076</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3405</v>
+        <v>3723</v>
       </c>
       <c r="C3" t="n">
-        <v>3452</v>
+        <v>5113</v>
       </c>
       <c r="D3" t="n">
-        <v>9152</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>2643</v>
       </c>
       <c r="C4" t="n">
-        <v>2626</v>
+        <v>3999</v>
       </c>
       <c r="D4" t="n">
-        <v>2997</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1035</v>
+        <v>1117</v>
       </c>
       <c r="C5" t="n">
-        <v>1437</v>
+        <v>3010</v>
       </c>
       <c r="D5" t="n">
-        <v>1399</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>503</v>
+        <v>1076</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>7612</v>
       </c>
       <c r="C2" t="n">
-        <v>6889</v>
+        <v>7066</v>
       </c>
       <c r="D2" t="n">
-        <v>24703</v>
+        <v>37987</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2949</v>
+        <v>3986</v>
       </c>
       <c r="C3" t="n">
-        <v>3712</v>
+        <v>6695</v>
       </c>
       <c r="D3" t="n">
-        <v>10834</v>
+        <v>12478</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1799</v>
+        <v>1952</v>
       </c>
       <c r="C4" t="n">
-        <v>2533</v>
+        <v>3765</v>
       </c>
       <c r="D4" t="n">
-        <v>3490</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>905</v>
+        <v>974</v>
       </c>
       <c r="C5" t="n">
-        <v>1500</v>
+        <v>2538</v>
       </c>
       <c r="D5" t="n">
-        <v>1336</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>662</v>
+        <v>1368</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>272</v>
+        <v>446</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4624</v>
+        <v>5731</v>
       </c>
       <c r="C2" t="n">
-        <v>4280</v>
+        <v>5425</v>
       </c>
       <c r="D2" t="n">
-        <v>20465</v>
+        <v>29643</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3400</v>
+        <v>4769</v>
       </c>
       <c r="C3" t="n">
-        <v>4829</v>
+        <v>5947</v>
       </c>
       <c r="D3" t="n">
-        <v>12460</v>
+        <v>15845</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2092</v>
+        <v>2563</v>
       </c>
       <c r="C4" t="n">
-        <v>3216</v>
+        <v>5430</v>
       </c>
       <c r="D4" t="n">
-        <v>4934</v>
+        <v>5695</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1206</v>
+        <v>1299</v>
       </c>
       <c r="C5" t="n">
-        <v>2093</v>
+        <v>3191</v>
       </c>
       <c r="D5" t="n">
-        <v>1716</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="C6" t="n">
-        <v>1144</v>
+        <v>2003</v>
       </c>
       <c r="D6" t="n">
-        <v>877</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>497</v>
+        <v>951</v>
       </c>
       <c r="D7" t="n">
         <v>565</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>251</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>196</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4820</v>
+        <v>5343</v>
       </c>
       <c r="C2" t="n">
-        <v>8459</v>
+        <v>7484</v>
       </c>
       <c r="D2" t="n">
-        <v>15481</v>
+        <v>27639</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3306</v>
+        <v>4313</v>
       </c>
       <c r="C3" t="n">
-        <v>3896</v>
+        <v>4928</v>
       </c>
       <c r="D3" t="n">
-        <v>12887</v>
+        <v>16826</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2386</v>
+        <v>3129</v>
       </c>
       <c r="C4" t="n">
-        <v>4093</v>
+        <v>5599</v>
       </c>
       <c r="D4" t="n">
-        <v>6301</v>
+        <v>7318</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1452</v>
+        <v>1664</v>
       </c>
       <c r="C5" t="n">
-        <v>2685</v>
+        <v>4276</v>
       </c>
       <c r="D5" t="n">
-        <v>2281</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="C6" t="n">
-        <v>1649</v>
+        <v>2596</v>
       </c>
       <c r="D6" t="n">
-        <v>1009</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>840</v>
+        <v>1486</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>634</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_23_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5743</v>
+        <v>5452</v>
       </c>
       <c r="C2" t="n">
-        <v>6903</v>
+        <v>14162</v>
       </c>
       <c r="D2" t="n">
-        <v>21270</v>
+        <v>28897</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3938</v>
+        <v>3430</v>
       </c>
       <c r="C3" t="n">
-        <v>5384</v>
+        <v>6471</v>
       </c>
       <c r="D3" t="n">
-        <v>17225</v>
+        <v>15906</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3163</v>
+        <v>2759</v>
       </c>
       <c r="C4" t="n">
-        <v>5093</v>
+        <v>5633</v>
       </c>
       <c r="D4" t="n">
-        <v>8738</v>
+        <v>7609</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2026</v>
+        <v>1795</v>
       </c>
       <c r="C5" t="n">
-        <v>4834</v>
+        <v>4989</v>
       </c>
       <c r="D5" t="n">
-        <v>3219</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1102</v>
+        <v>1040</v>
       </c>
       <c r="C6" t="n">
-        <v>3334</v>
+        <v>3881</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="C7" t="n">
-        <v>2007</v>
+        <v>2344</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -881,7 +881,7 @@
         <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>430</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
         <v>301</v>
@@ -895,10 +895,10 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -968,7 +968,7 @@
         <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7759</v>
+        <v>6050</v>
       </c>
       <c r="C2" t="n">
-        <v>11536</v>
+        <v>17830</v>
       </c>
       <c r="D2" t="n">
-        <v>34203</v>
+        <v>36279</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3850</v>
+        <v>3498</v>
       </c>
       <c r="C3" t="n">
-        <v>5338</v>
+        <v>8668</v>
       </c>
       <c r="D3" t="n">
-        <v>16612</v>
+        <v>16525</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2985</v>
+        <v>2626</v>
       </c>
       <c r="C4" t="n">
-        <v>5072</v>
+        <v>5901</v>
       </c>
       <c r="D4" t="n">
-        <v>9692</v>
+        <v>8579</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2230</v>
+        <v>1938</v>
       </c>
       <c r="C5" t="n">
-        <v>4850</v>
+        <v>5121</v>
       </c>
       <c r="D5" t="n">
-        <v>3968</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1344</v>
+        <v>1228</v>
       </c>
       <c r="C6" t="n">
-        <v>3917</v>
+        <v>4323</v>
       </c>
       <c r="D6" t="n">
-        <v>1529</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>671</v>
+        <v>637</v>
       </c>
       <c r="C7" t="n">
-        <v>2578</v>
+        <v>2967</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C8" t="n">
-        <v>1410</v>
+        <v>1558</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>663</v>
+        <v>628</v>
       </c>
       <c r="D9" t="n">
         <v>315</v>
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -1293,7 +1293,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8081</v>
+        <v>7845</v>
       </c>
       <c r="C2" t="n">
-        <v>12963</v>
+        <v>11533</v>
       </c>
       <c r="D2" t="n">
-        <v>35569</v>
+        <v>31379</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4333</v>
+        <v>3649</v>
       </c>
       <c r="C3" t="n">
-        <v>6930</v>
+        <v>10876</v>
       </c>
       <c r="D3" t="n">
-        <v>17659</v>
+        <v>17837</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2833</v>
+        <v>2527</v>
       </c>
       <c r="C4" t="n">
-        <v>5078</v>
+        <v>6863</v>
       </c>
       <c r="D4" t="n">
-        <v>10393</v>
+        <v>9462</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2250</v>
+        <v>1982</v>
       </c>
       <c r="C5" t="n">
-        <v>4792</v>
+        <v>5328</v>
       </c>
       <c r="D5" t="n">
-        <v>4578</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1532</v>
+        <v>1362</v>
       </c>
       <c r="C6" t="n">
-        <v>4212</v>
+        <v>4550</v>
       </c>
       <c r="D6" t="n">
-        <v>1836</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="C7" t="n">
-        <v>3101</v>
+        <v>3454</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
-        <v>1830</v>
+        <v>2082</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>927</v>
+        <v>949</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1548,7 +1548,7 @@
         <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1604,7 +1604,7 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7470</v>
+        <v>7154</v>
       </c>
       <c r="C2" t="n">
-        <v>9022</v>
+        <v>8119</v>
       </c>
       <c r="D2" t="n">
-        <v>29302</v>
+        <v>25959</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5108</v>
+        <v>4391</v>
       </c>
       <c r="C3" t="n">
-        <v>10145</v>
+        <v>14512</v>
       </c>
       <c r="D3" t="n">
-        <v>19297</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2079</v>
+        <v>1831</v>
       </c>
       <c r="C4" t="n">
-        <v>7330</v>
+        <v>8738</v>
       </c>
       <c r="D4" t="n">
-        <v>9948</v>
+        <v>9057</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1415</v>
+        <v>1258</v>
       </c>
       <c r="C5" t="n">
-        <v>4127</v>
+        <v>4459</v>
       </c>
       <c r="D5" t="n">
-        <v>3029</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>767</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>3038</v>
+        <v>3384</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>801</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1793</v>
+        <v>2040</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1828,7 +1828,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1901,7 +1901,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4560</v>
+        <v>4449</v>
       </c>
       <c r="C2" t="n">
-        <v>3863</v>
+        <v>4427</v>
       </c>
       <c r="D2" t="n">
-        <v>20727</v>
+        <v>18488</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5246</v>
+        <v>4718</v>
       </c>
       <c r="C3" t="n">
-        <v>8770</v>
+        <v>10705</v>
       </c>
       <c r="D3" t="n">
-        <v>19731</v>
+        <v>18968</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2782</v>
+        <v>2398</v>
       </c>
       <c r="C4" t="n">
-        <v>8729</v>
+        <v>11357</v>
       </c>
       <c r="D4" t="n">
-        <v>11182</v>
+        <v>10412</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1575</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>5460</v>
+        <v>6264</v>
       </c>
       <c r="D5" t="n">
-        <v>3792</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>834</v>
       </c>
       <c r="C6" t="n">
-        <v>3589</v>
+        <v>3942</v>
       </c>
       <c r="D6" t="n">
-        <v>1026</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>2250</v>
+        <v>2528</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1190</v>
+        <v>1227</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -2125,7 +2125,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4310</v>
+        <v>3962</v>
       </c>
       <c r="C2" t="n">
-        <v>4195</v>
+        <v>12022</v>
       </c>
       <c r="D2" t="n">
-        <v>16494</v>
+        <v>17137</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4177</v>
+        <v>3911</v>
       </c>
       <c r="C3" t="n">
-        <v>5754</v>
+        <v>6976</v>
       </c>
       <c r="D3" t="n">
-        <v>18540</v>
+        <v>17810</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3257</v>
+        <v>2854</v>
       </c>
       <c r="C4" t="n">
-        <v>8567</v>
+        <v>10814</v>
       </c>
       <c r="D4" t="n">
-        <v>12237</v>
+        <v>11309</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>1598</v>
       </c>
       <c r="C5" t="n">
-        <v>6905</v>
+        <v>8491</v>
       </c>
       <c r="D5" t="n">
-        <v>4811</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1085</v>
+        <v>965</v>
       </c>
       <c r="C6" t="n">
-        <v>4363</v>
+        <v>4886</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>2835</v>
+        <v>3133</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>1616</v>
+        <v>1735</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2607</v>
+        <v>2439</v>
       </c>
       <c r="C2" t="n">
-        <v>2030</v>
+        <v>5897</v>
       </c>
       <c r="D2" t="n">
-        <v>11505</v>
+        <v>12112</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4097</v>
+        <v>3789</v>
       </c>
       <c r="C3" t="n">
-        <v>5076</v>
+        <v>8371</v>
       </c>
       <c r="D3" t="n">
-        <v>17911</v>
+        <v>17374</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3560</v>
+        <v>3122</v>
       </c>
       <c r="C4" t="n">
-        <v>8402</v>
+        <v>10485</v>
       </c>
       <c r="D4" t="n">
-        <v>13043</v>
+        <v>12092</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1918</v>
+        <v>1668</v>
       </c>
       <c r="C5" t="n">
-        <v>8307</v>
+        <v>10262</v>
       </c>
       <c r="D5" t="n">
-        <v>5076</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>5186</v>
+        <v>5724</v>
       </c>
       <c r="D6" t="n">
-        <v>1372</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2942</v>
+        <v>3202</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3264</v>
+        <v>2435</v>
       </c>
       <c r="C2" t="n">
-        <v>4439</v>
+        <v>4329</v>
       </c>
       <c r="D2" t="n">
-        <v>18799</v>
+        <v>11467</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2998</v>
+        <v>2794</v>
       </c>
       <c r="C3" t="n">
-        <v>3329</v>
+        <v>6476</v>
       </c>
       <c r="D3" t="n">
-        <v>16008</v>
+        <v>15560</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3297</v>
+        <v>2976</v>
       </c>
       <c r="C4" t="n">
-        <v>6775</v>
+        <v>9413</v>
       </c>
       <c r="D4" t="n">
-        <v>13394</v>
+        <v>12535</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2284</v>
+        <v>1956</v>
       </c>
       <c r="C5" t="n">
-        <v>8175</v>
+        <v>10241</v>
       </c>
       <c r="D5" t="n">
-        <v>6068</v>
+        <v>5519</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1004</v>
       </c>
       <c r="C6" t="n">
-        <v>6529</v>
+        <v>7517</v>
       </c>
       <c r="D6" t="n">
-        <v>1865</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>3827</v>
+        <v>4202</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1826</v>
+        <v>1881</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2385</v>
+        <v>1760</v>
       </c>
       <c r="C2" t="n">
-        <v>3106</v>
+        <v>2749</v>
       </c>
       <c r="D2" t="n">
-        <v>15088</v>
+        <v>8797</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2701</v>
+        <v>2356</v>
       </c>
       <c r="C3" t="n">
-        <v>3412</v>
+        <v>5246</v>
       </c>
       <c r="D3" t="n">
-        <v>15475</v>
+        <v>14280</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2959</v>
+        <v>2694</v>
       </c>
       <c r="C4" t="n">
-        <v>5472</v>
+        <v>8298</v>
       </c>
       <c r="D4" t="n">
-        <v>13441</v>
+        <v>12651</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2447</v>
+        <v>2133</v>
       </c>
       <c r="C5" t="n">
-        <v>7756</v>
+        <v>10143</v>
       </c>
       <c r="D5" t="n">
-        <v>6773</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1335</v>
+        <v>1134</v>
       </c>
       <c r="C6" t="n">
-        <v>7295</v>
+        <v>8597</v>
       </c>
       <c r="D6" t="n">
-        <v>2202</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>4723</v>
+        <v>5203</v>
       </c>
       <c r="D7" t="n">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2314</v>
+        <v>2379</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>659</v>
+        <v>592</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3105</v>
+        <v>2373</v>
       </c>
       <c r="C2" t="n">
-        <v>10342</v>
+        <v>6446</v>
       </c>
       <c r="D2" t="n">
-        <v>22124</v>
+        <v>10605</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2182</v>
+        <v>1823</v>
       </c>
       <c r="C3" t="n">
-        <v>2935</v>
+        <v>3894</v>
       </c>
       <c r="D3" t="n">
-        <v>14586</v>
+        <v>12774</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2494</v>
+        <v>2246</v>
       </c>
       <c r="C4" t="n">
-        <v>4507</v>
+        <v>6924</v>
       </c>
       <c r="D4" t="n">
-        <v>13176</v>
+        <v>12485</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2414</v>
+        <v>2110</v>
       </c>
       <c r="C5" t="n">
-        <v>6695</v>
+        <v>9241</v>
       </c>
       <c r="D5" t="n">
-        <v>7463</v>
+        <v>6814</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1578</v>
+        <v>1346</v>
       </c>
       <c r="C6" t="n">
-        <v>7407</v>
+        <v>9079</v>
       </c>
       <c r="D6" t="n">
-        <v>2744</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>451</v>
       </c>
       <c r="C7" t="n">
-        <v>5653</v>
+        <v>6365</v>
       </c>
       <c r="D7" t="n">
-        <v>911</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>3162</v>
+        <v>3291</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1184</v>
+        <v>1140</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6464</v>
+        <v>6603</v>
       </c>
       <c r="C2" t="n">
-        <v>10927</v>
+        <v>7671</v>
       </c>
       <c r="D2" t="n">
-        <v>15992</v>
+        <v>15316</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2247</v>
+        <v>1754</v>
       </c>
       <c r="C2" t="n">
-        <v>6040</v>
+        <v>3867</v>
       </c>
       <c r="D2" t="n">
-        <v>16461</v>
+        <v>7890</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2936</v>
+        <v>2470</v>
       </c>
       <c r="C3" t="n">
-        <v>4797</v>
+        <v>4898</v>
       </c>
       <c r="D3" t="n">
-        <v>16126</v>
+        <v>13815</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3482</v>
+        <v>3097</v>
       </c>
       <c r="C4" t="n">
-        <v>6765</v>
+        <v>9880</v>
       </c>
       <c r="D4" t="n">
-        <v>13554</v>
+        <v>12727</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>1243</v>
       </c>
       <c r="C5" t="n">
-        <v>10121</v>
+        <v>13151</v>
       </c>
       <c r="D5" t="n">
-        <v>6744</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="C6" t="n">
-        <v>6919</v>
+        <v>7750</v>
       </c>
       <c r="D6" t="n">
-        <v>2094</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>3098</v>
+        <v>3225</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1160</v>
+        <v>1117</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6775</v>
+        <v>6896</v>
       </c>
       <c r="C2" t="n">
-        <v>5995</v>
+        <v>9825</v>
       </c>
       <c r="D2" t="n">
-        <v>22395</v>
+        <v>19236</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2746</v>
+        <v>2805</v>
       </c>
       <c r="C3" t="n">
-        <v>5507</v>
+        <v>3866</v>
       </c>
       <c r="D3" t="n">
-        <v>3325</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6219</v>
+        <v>4831</v>
       </c>
       <c r="C2" t="n">
-        <v>4500</v>
+        <v>9519</v>
       </c>
       <c r="D2" t="n">
-        <v>24125</v>
+        <v>22228</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3910</v>
+        <v>3984</v>
       </c>
       <c r="C3" t="n">
-        <v>4987</v>
+        <v>6242</v>
       </c>
       <c r="D3" t="n">
-        <v>6284</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1227</v>
+        <v>1253</v>
       </c>
       <c r="C4" t="n">
-        <v>3270</v>
+        <v>2309</v>
       </c>
       <c r="D4" t="n">
-        <v>1851</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4906</v>
+        <v>5168</v>
       </c>
       <c r="C2" t="n">
-        <v>7599</v>
+        <v>8142</v>
       </c>
       <c r="D2" t="n">
-        <v>22680</v>
+        <v>24381</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4170</v>
+        <v>3624</v>
       </c>
       <c r="C3" t="n">
-        <v>4098</v>
+        <v>6933</v>
       </c>
       <c r="D3" t="n">
-        <v>8686</v>
+        <v>7908</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2153</v>
+        <v>2229</v>
       </c>
       <c r="C4" t="n">
-        <v>4158</v>
+        <v>4428</v>
       </c>
       <c r="D4" t="n">
-        <v>2645</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="C5" t="n">
-        <v>1855</v>
+        <v>1360</v>
       </c>
       <c r="D5" t="n">
-        <v>1269</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7482</v>
+        <v>5834</v>
       </c>
       <c r="C2" t="n">
-        <v>11208</v>
+        <v>8223</v>
       </c>
       <c r="D2" t="n">
-        <v>35076</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3723</v>
+        <v>3569</v>
       </c>
       <c r="C3" t="n">
-        <v>5113</v>
+        <v>6577</v>
       </c>
       <c r="D3" t="n">
-        <v>10201</v>
+        <v>9855</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2643</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>3999</v>
+        <v>5658</v>
       </c>
       <c r="D4" t="n">
-        <v>3666</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1117</v>
+        <v>1132</v>
       </c>
       <c r="C5" t="n">
-        <v>3010</v>
+        <v>2879</v>
       </c>
       <c r="D5" t="n">
-        <v>1456</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>1076</v>
+        <v>828</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>666</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7612</v>
+        <v>6360</v>
       </c>
       <c r="C2" t="n">
-        <v>7066</v>
+        <v>6713</v>
       </c>
       <c r="D2" t="n">
-        <v>37987</v>
+        <v>23816</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3986</v>
+        <v>3370</v>
       </c>
       <c r="C3" t="n">
-        <v>6695</v>
+        <v>6068</v>
       </c>
       <c r="D3" t="n">
-        <v>12478</v>
+        <v>11341</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1952</v>
+        <v>1855</v>
       </c>
       <c r="C4" t="n">
-        <v>3765</v>
+        <v>5035</v>
       </c>
       <c r="D4" t="n">
-        <v>4140</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>974</v>
+        <v>941</v>
       </c>
       <c r="C5" t="n">
-        <v>2538</v>
+        <v>3115</v>
       </c>
       <c r="D5" t="n">
-        <v>1452</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C6" t="n">
-        <v>1368</v>
+        <v>1239</v>
       </c>
       <c r="D6" t="n">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>446</v>
+        <v>368</v>
       </c>
       <c r="D7" t="n">
         <v>523</v>
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5874,7 +5874,7 @@
         <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5731</v>
+        <v>5280</v>
       </c>
       <c r="C2" t="n">
-        <v>5425</v>
+        <v>8517</v>
       </c>
       <c r="D2" t="n">
-        <v>29643</v>
+        <v>30655</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4769</v>
+        <v>4023</v>
       </c>
       <c r="C3" t="n">
-        <v>5947</v>
+        <v>5543</v>
       </c>
       <c r="D3" t="n">
-        <v>15845</v>
+        <v>12602</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2563</v>
+        <v>2283</v>
       </c>
       <c r="C4" t="n">
-        <v>5430</v>
+        <v>5545</v>
       </c>
       <c r="D4" t="n">
-        <v>5695</v>
+        <v>5293</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1299</v>
+        <v>1242</v>
       </c>
       <c r="C5" t="n">
-        <v>3191</v>
+        <v>4156</v>
       </c>
       <c r="D5" t="n">
-        <v>1910</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C6" t="n">
-        <v>2003</v>
+        <v>2268</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>951</v>
+        <v>842</v>
       </c>
       <c r="D7" t="n">
         <v>565</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6185,7 +6185,7 @@
         <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5343</v>
+        <v>4582</v>
       </c>
       <c r="C2" t="n">
-        <v>7484</v>
+        <v>8721</v>
       </c>
       <c r="D2" t="n">
-        <v>27639</v>
+        <v>31428</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4313</v>
+        <v>3809</v>
       </c>
       <c r="C3" t="n">
-        <v>4928</v>
+        <v>6171</v>
       </c>
       <c r="D3" t="n">
-        <v>16826</v>
+        <v>14458</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3129</v>
+        <v>2695</v>
       </c>
       <c r="C4" t="n">
-        <v>5599</v>
+        <v>5428</v>
       </c>
       <c r="D4" t="n">
-        <v>7318</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1664</v>
+        <v>1525</v>
       </c>
       <c r="C5" t="n">
-        <v>4276</v>
+        <v>4763</v>
       </c>
       <c r="D5" t="n">
-        <v>2542</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>821</v>
       </c>
       <c r="C6" t="n">
-        <v>2596</v>
+        <v>3221</v>
       </c>
       <c r="D6" t="n">
-        <v>1052</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>1486</v>
+        <v>1568</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>634</v>
+        <v>562</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
@@ -6566,7 +6566,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>

--- a/output/yearly_population_iteration_23_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_23_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5452</v>
+        <v>1293</v>
       </c>
       <c r="C2" t="n">
-        <v>14162</v>
+        <v>2623</v>
       </c>
       <c r="D2" t="n">
-        <v>28897</v>
+        <v>17270</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3430</v>
+        <v>1929</v>
       </c>
       <c r="C3" t="n">
-        <v>6471</v>
+        <v>5381</v>
       </c>
       <c r="D3" t="n">
-        <v>15906</v>
+        <v>14132</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2759</v>
+        <v>1250</v>
       </c>
       <c r="C4" t="n">
-        <v>5633</v>
+        <v>6899</v>
       </c>
       <c r="D4" t="n">
-        <v>7609</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1795</v>
+        <v>666</v>
       </c>
       <c r="C5" t="n">
-        <v>4989</v>
+        <v>4642</v>
       </c>
       <c r="D5" t="n">
-        <v>2960</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>284</v>
       </c>
       <c r="C6" t="n">
-        <v>3881</v>
+        <v>1785</v>
       </c>
       <c r="D6" t="n">
-        <v>1237</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>486</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>2344</v>
+        <v>633</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1009</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6050</v>
+        <v>1475</v>
       </c>
       <c r="C2" t="n">
-        <v>17830</v>
+        <v>10712</v>
       </c>
       <c r="D2" t="n">
-        <v>36279</v>
+        <v>13482</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3498</v>
+        <v>1367</v>
       </c>
       <c r="C3" t="n">
-        <v>8668</v>
+        <v>3386</v>
       </c>
       <c r="D3" t="n">
-        <v>16525</v>
+        <v>13752</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2626</v>
+        <v>1368</v>
       </c>
       <c r="C4" t="n">
-        <v>5901</v>
+        <v>5976</v>
       </c>
       <c r="D4" t="n">
-        <v>8579</v>
+        <v>7256</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1938</v>
+        <v>831</v>
       </c>
       <c r="C5" t="n">
-        <v>5121</v>
+        <v>5781</v>
       </c>
       <c r="D5" t="n">
-        <v>3584</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1228</v>
+        <v>417</v>
       </c>
       <c r="C6" t="n">
-        <v>4323</v>
+        <v>3191</v>
       </c>
       <c r="D6" t="n">
-        <v>1456</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>637</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>2967</v>
+        <v>1209</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1558</v>
+        <v>476</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>628</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7845</v>
+        <v>772</v>
       </c>
       <c r="C2" t="n">
-        <v>11533</v>
+        <v>4410</v>
       </c>
       <c r="D2" t="n">
-        <v>31379</v>
+        <v>9101</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3649</v>
+        <v>1344</v>
       </c>
       <c r="C3" t="n">
-        <v>10876</v>
+        <v>6084</v>
       </c>
       <c r="D3" t="n">
-        <v>17837</v>
+        <v>13343</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2527</v>
+        <v>1513</v>
       </c>
       <c r="C4" t="n">
-        <v>6863</v>
+        <v>5438</v>
       </c>
       <c r="D4" t="n">
-        <v>9462</v>
+        <v>8132</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1982</v>
+        <v>849</v>
       </c>
       <c r="C5" t="n">
-        <v>5328</v>
+        <v>6547</v>
       </c>
       <c r="D5" t="n">
-        <v>4111</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1362</v>
+        <v>334</v>
       </c>
       <c r="C6" t="n">
-        <v>4550</v>
+        <v>4101</v>
       </c>
       <c r="D6" t="n">
-        <v>1723</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>769</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3454</v>
+        <v>1170</v>
       </c>
       <c r="D7" t="n">
-        <v>818</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2082</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>949</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7154</v>
+        <v>789</v>
       </c>
       <c r="C2" t="n">
-        <v>8119</v>
+        <v>3098</v>
       </c>
       <c r="D2" t="n">
-        <v>25959</v>
+        <v>9188</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4391</v>
+        <v>913</v>
       </c>
       <c r="C3" t="n">
-        <v>14512</v>
+        <v>4580</v>
       </c>
       <c r="D3" t="n">
-        <v>19174</v>
+        <v>11758</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1831</v>
+        <v>1275</v>
       </c>
       <c r="C4" t="n">
-        <v>8738</v>
+        <v>5724</v>
       </c>
       <c r="D4" t="n">
-        <v>9057</v>
+        <v>8913</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1258</v>
+        <v>1022</v>
       </c>
       <c r="C5" t="n">
-        <v>4459</v>
+        <v>5909</v>
       </c>
       <c r="D5" t="n">
-        <v>2754</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>500</v>
       </c>
       <c r="C6" t="n">
-        <v>3384</v>
+        <v>5312</v>
       </c>
       <c r="D6" t="n">
-        <v>801</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>2040</v>
+        <v>2513</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>930</v>
+        <v>773</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4449</v>
+        <v>407</v>
       </c>
       <c r="C2" t="n">
-        <v>4427</v>
+        <v>1593</v>
       </c>
       <c r="D2" t="n">
-        <v>18488</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4718</v>
+        <v>756</v>
       </c>
       <c r="C3" t="n">
-        <v>10705</v>
+        <v>3531</v>
       </c>
       <c r="D3" t="n">
-        <v>18968</v>
+        <v>10731</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2398</v>
+        <v>1062</v>
       </c>
       <c r="C4" t="n">
-        <v>11357</v>
+        <v>5231</v>
       </c>
       <c r="D4" t="n">
-        <v>10412</v>
+        <v>9164</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>1078</v>
       </c>
       <c r="C5" t="n">
-        <v>6264</v>
+        <v>5934</v>
       </c>
       <c r="D5" t="n">
-        <v>3449</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>834</v>
+        <v>613</v>
       </c>
       <c r="C6" t="n">
-        <v>3942</v>
+        <v>5747</v>
       </c>
       <c r="D6" t="n">
-        <v>983</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>2528</v>
+        <v>3534</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3962</v>
+        <v>1302</v>
       </c>
       <c r="C2" t="n">
-        <v>12022</v>
+        <v>6872</v>
       </c>
       <c r="D2" t="n">
-        <v>17137</v>
+        <v>15525</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3911</v>
+        <v>513</v>
       </c>
       <c r="C3" t="n">
-        <v>6976</v>
+        <v>2323</v>
       </c>
       <c r="D3" t="n">
-        <v>17810</v>
+        <v>9543</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2854</v>
+        <v>822</v>
       </c>
       <c r="C4" t="n">
-        <v>10814</v>
+        <v>4289</v>
       </c>
       <c r="D4" t="n">
-        <v>11309</v>
+        <v>9141</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1598</v>
+        <v>990</v>
       </c>
       <c r="C5" t="n">
-        <v>8491</v>
+        <v>5479</v>
       </c>
       <c r="D5" t="n">
-        <v>4413</v>
+        <v>5022</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>965</v>
+        <v>738</v>
       </c>
       <c r="C6" t="n">
-        <v>4886</v>
+        <v>5831</v>
       </c>
       <c r="D6" t="n">
-        <v>1325</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>3133</v>
+        <v>4521</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1735</v>
+        <v>2151</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>710</v>
+        <v>748</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2439</v>
+        <v>864</v>
       </c>
       <c r="C2" t="n">
-        <v>5897</v>
+        <v>3518</v>
       </c>
       <c r="D2" t="n">
-        <v>12112</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3789</v>
+        <v>838</v>
       </c>
       <c r="C3" t="n">
-        <v>8371</v>
+        <v>3807</v>
       </c>
       <c r="D3" t="n">
-        <v>17374</v>
+        <v>10750</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3122</v>
+        <v>1317</v>
       </c>
       <c r="C4" t="n">
-        <v>10485</v>
+        <v>5886</v>
       </c>
       <c r="D4" t="n">
-        <v>12092</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1668</v>
+        <v>755</v>
       </c>
       <c r="C5" t="n">
-        <v>10262</v>
+        <v>8120</v>
       </c>
       <c r="D5" t="n">
-        <v>4524</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>5724</v>
+        <v>5916</v>
       </c>
       <c r="D6" t="n">
-        <v>1291</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>3202</v>
+        <v>2107</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1188</v>
+        <v>733</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2435</v>
+        <v>424</v>
       </c>
       <c r="C2" t="n">
-        <v>4329</v>
+        <v>1705</v>
       </c>
       <c r="D2" t="n">
-        <v>11467</v>
+        <v>8419</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2794</v>
+        <v>719</v>
       </c>
       <c r="C3" t="n">
-        <v>6476</v>
+        <v>3220</v>
       </c>
       <c r="D3" t="n">
-        <v>15560</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2976</v>
+        <v>910</v>
       </c>
       <c r="C4" t="n">
-        <v>9413</v>
+        <v>4559</v>
       </c>
       <c r="D4" t="n">
-        <v>12535</v>
+        <v>9071</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1956</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>10241</v>
+        <v>6261</v>
       </c>
       <c r="D5" t="n">
-        <v>5519</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1004</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>7517</v>
+        <v>5654</v>
       </c>
       <c r="D6" t="n">
-        <v>1677</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>4202</v>
+        <v>2745</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1881</v>
+        <v>827</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>555</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1760</v>
+        <v>245</v>
       </c>
       <c r="C2" t="n">
-        <v>2749</v>
+        <v>5241</v>
       </c>
       <c r="D2" t="n">
-        <v>8797</v>
+        <v>9481</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2356</v>
+        <v>484</v>
       </c>
       <c r="C3" t="n">
-        <v>5246</v>
+        <v>2085</v>
       </c>
       <c r="D3" t="n">
-        <v>14280</v>
+        <v>9057</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2694</v>
+        <v>712</v>
       </c>
       <c r="C4" t="n">
-        <v>8298</v>
+        <v>3705</v>
       </c>
       <c r="D4" t="n">
-        <v>12651</v>
+        <v>8981</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2133</v>
+        <v>730</v>
       </c>
       <c r="C5" t="n">
-        <v>10143</v>
+        <v>5259</v>
       </c>
       <c r="D5" t="n">
-        <v>6198</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1134</v>
+        <v>431</v>
       </c>
       <c r="C6" t="n">
-        <v>8597</v>
+        <v>5905</v>
       </c>
       <c r="D6" t="n">
-        <v>1985</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>5203</v>
+        <v>4253</v>
       </c>
       <c r="D7" t="n">
-        <v>739</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>2379</v>
+        <v>1755</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>529</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2373</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>6446</v>
+        <v>16651</v>
       </c>
       <c r="D2" t="n">
-        <v>10605</v>
+        <v>12156</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1823</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>3894</v>
+        <v>3226</v>
       </c>
       <c r="D3" t="n">
-        <v>12774</v>
+        <v>8570</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2246</v>
+        <v>531</v>
       </c>
       <c r="C4" t="n">
-        <v>6924</v>
+        <v>2752</v>
       </c>
       <c r="D4" t="n">
-        <v>12485</v>
+        <v>8634</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2110</v>
+        <v>652</v>
       </c>
       <c r="C5" t="n">
-        <v>9241</v>
+        <v>4358</v>
       </c>
       <c r="D5" t="n">
-        <v>6814</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1346</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>9079</v>
+        <v>5526</v>
       </c>
       <c r="D6" t="n">
-        <v>2425</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>6365</v>
+        <v>5044</v>
       </c>
       <c r="D7" t="n">
-        <v>877</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>3291</v>
+        <v>2904</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1140</v>
+        <v>1069</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6603</v>
+        <v>4271</v>
       </c>
       <c r="C2" t="n">
-        <v>7671</v>
+        <v>6915</v>
       </c>
       <c r="D2" t="n">
-        <v>15316</v>
+        <v>18965</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1754</v>
+        <v>569</v>
       </c>
       <c r="C2" t="n">
-        <v>3867</v>
+        <v>14908</v>
       </c>
       <c r="D2" t="n">
-        <v>7890</v>
+        <v>13831</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2470</v>
+        <v>217</v>
       </c>
       <c r="C3" t="n">
-        <v>4898</v>
+        <v>8239</v>
       </c>
       <c r="D3" t="n">
-        <v>13815</v>
+        <v>8481</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3097</v>
+        <v>381</v>
       </c>
       <c r="C4" t="n">
-        <v>9880</v>
+        <v>2891</v>
       </c>
       <c r="D4" t="n">
-        <v>12727</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1243</v>
+        <v>554</v>
       </c>
       <c r="C5" t="n">
-        <v>13151</v>
+        <v>3527</v>
       </c>
       <c r="D5" t="n">
-        <v>6052</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>416</v>
+        <v>532</v>
       </c>
       <c r="C6" t="n">
-        <v>7750</v>
+        <v>4957</v>
       </c>
       <c r="D6" t="n">
-        <v>1920</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>3225</v>
+        <v>5200</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>1117</v>
+        <v>3804</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>1805</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>612</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6896</v>
+        <v>4816</v>
       </c>
       <c r="C2" t="n">
-        <v>9825</v>
+        <v>9984</v>
       </c>
       <c r="D2" t="n">
-        <v>19236</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2805</v>
+        <v>1378</v>
       </c>
       <c r="C3" t="n">
-        <v>3866</v>
+        <v>2730</v>
       </c>
       <c r="D3" t="n">
-        <v>3212</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4831</v>
+        <v>2715</v>
       </c>
       <c r="C2" t="n">
-        <v>9519</v>
+        <v>6354</v>
       </c>
       <c r="D2" t="n">
-        <v>22228</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3984</v>
+        <v>2620</v>
       </c>
       <c r="C3" t="n">
-        <v>6242</v>
+        <v>6108</v>
       </c>
       <c r="D3" t="n">
-        <v>5667</v>
+        <v>5663</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1253</v>
+        <v>663</v>
       </c>
       <c r="C4" t="n">
-        <v>2309</v>
+        <v>1751</v>
       </c>
       <c r="D4" t="n">
-        <v>1828</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>344</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5168</v>
+        <v>1615</v>
       </c>
       <c r="C2" t="n">
-        <v>8142</v>
+        <v>5189</v>
       </c>
       <c r="D2" t="n">
-        <v>24381</v>
+        <v>15255</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3624</v>
+        <v>2200</v>
       </c>
       <c r="C3" t="n">
-        <v>6933</v>
+        <v>5379</v>
       </c>
       <c r="D3" t="n">
-        <v>7908</v>
+        <v>7234</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2229</v>
+        <v>1443</v>
       </c>
       <c r="C4" t="n">
-        <v>4428</v>
+        <v>4307</v>
       </c>
       <c r="D4" t="n">
-        <v>2509</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>564</v>
+        <v>330</v>
       </c>
       <c r="C5" t="n">
-        <v>1360</v>
+        <v>1092</v>
       </c>
       <c r="D5" t="n">
-        <v>1264</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>333</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5834</v>
+        <v>1473</v>
       </c>
       <c r="C2" t="n">
-        <v>8223</v>
+        <v>6091</v>
       </c>
       <c r="D2" t="n">
-        <v>28894</v>
+        <v>25475</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3569</v>
+        <v>1583</v>
       </c>
       <c r="C3" t="n">
-        <v>6577</v>
+        <v>4556</v>
       </c>
       <c r="D3" t="n">
-        <v>9855</v>
+        <v>7996</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>1576</v>
       </c>
       <c r="C4" t="n">
-        <v>5658</v>
+        <v>4834</v>
       </c>
       <c r="D4" t="n">
-        <v>3417</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1132</v>
+        <v>754</v>
       </c>
       <c r="C5" t="n">
-        <v>2879</v>
+        <v>2859</v>
       </c>
       <c r="D5" t="n">
-        <v>1428</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>303</v>
+        <v>196</v>
       </c>
       <c r="C6" t="n">
-        <v>828</v>
+        <v>705</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6360</v>
+        <v>2549</v>
       </c>
       <c r="C2" t="n">
-        <v>6713</v>
+        <v>4337</v>
       </c>
       <c r="D2" t="n">
-        <v>23816</v>
+        <v>24202</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3370</v>
+        <v>1268</v>
       </c>
       <c r="C3" t="n">
-        <v>6068</v>
+        <v>4653</v>
       </c>
       <c r="D3" t="n">
-        <v>11341</v>
+        <v>10089</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1855</v>
+        <v>1372</v>
       </c>
       <c r="C4" t="n">
-        <v>5035</v>
+        <v>4537</v>
       </c>
       <c r="D4" t="n">
-        <v>3915</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>941</v>
+        <v>994</v>
       </c>
       <c r="C5" t="n">
-        <v>3115</v>
+        <v>3842</v>
       </c>
       <c r="D5" t="n">
-        <v>1399</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>332</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>1239</v>
+        <v>1793</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>368</v>
+        <v>499</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5280</v>
+        <v>2774</v>
       </c>
       <c r="C2" t="n">
-        <v>8517</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="n">
-        <v>30655</v>
+        <v>32305</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4023</v>
+        <v>1502</v>
       </c>
       <c r="C3" t="n">
-        <v>5543</v>
+        <v>3938</v>
       </c>
       <c r="D3" t="n">
-        <v>12602</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2283</v>
+        <v>1141</v>
       </c>
       <c r="C4" t="n">
-        <v>5545</v>
+        <v>4501</v>
       </c>
       <c r="D4" t="n">
-        <v>5293</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>1044</v>
       </c>
       <c r="C5" t="n">
-        <v>4156</v>
+        <v>4065</v>
       </c>
       <c r="D5" t="n">
-        <v>1826</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="C6" t="n">
-        <v>2268</v>
+        <v>2757</v>
       </c>
       <c r="D6" t="n">
-        <v>886</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>842</v>
+        <v>1107</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4582</v>
+        <v>2462</v>
       </c>
       <c r="C2" t="n">
-        <v>8721</v>
+        <v>5211</v>
       </c>
       <c r="D2" t="n">
-        <v>31428</v>
+        <v>25288</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>2008</v>
       </c>
       <c r="C3" t="n">
-        <v>6171</v>
+        <v>6806</v>
       </c>
       <c r="D3" t="n">
-        <v>14458</v>
+        <v>12912</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2695</v>
+        <v>964</v>
       </c>
       <c r="C4" t="n">
-        <v>5428</v>
+        <v>6754</v>
       </c>
       <c r="D4" t="n">
-        <v>6414</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1525</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>4763</v>
+        <v>2701</v>
       </c>
       <c r="D5" t="n">
-        <v>2402</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>821</v>
+        <v>210</v>
       </c>
       <c r="C6" t="n">
-        <v>3221</v>
+        <v>1084</v>
       </c>
       <c r="D6" t="n">
-        <v>1027</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1568</v>
+        <v>379</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>562</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
